--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1022,6 +1022,103 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131996457</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91861</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>566774</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6521615</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonatan Axelsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jonatan Axelsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>131996457</v>
       </c>
       <c r="B5" t="n">
-        <v>91861</v>
+        <v>91862</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>131996457</v>
       </c>
       <c r="B5" t="n">
-        <v>91862</v>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>131996457</v>
       </c>
       <c r="B5" t="n">
-        <v>91910</v>
+        <v>91913</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>131996457</v>
       </c>
       <c r="B5" t="n">
-        <v>91913</v>
+        <v>91919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>131996457</v>
       </c>
       <c r="B5" t="n">
-        <v>91919</v>
+        <v>91929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -1027,7 +1027,7 @@
         <v>131996457</v>
       </c>
       <c r="B5" t="n">
-        <v>91929</v>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>92007171</v>
+        <v>100083913</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+          <t>Kolmården, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>566841.1919209226</v>
+        <v>566891</v>
       </c>
       <c r="R2" t="n">
-        <v>6521636.978031369</v>
+        <v>6521657</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-10-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-12-01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,38 +754,33 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Caroline Ryding</t>
+          <t>Helene Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kaj Almqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Holmen</t>
-        </is>
-      </c>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>97570874</v>
+        <v>97571121</v>
       </c>
       <c r="B3" t="n">
-        <v>88488</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>889</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Irpicodon pendulus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Pouzar</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>566820.9045407334</v>
+        <v>566757</v>
       </c>
       <c r="R3" t="n">
-        <v>6521580.184055927</v>
+        <v>6521664</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,22 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-04-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-04-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,53 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100083913</v>
+        <v>97570874</v>
       </c>
       <c r="B4" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>210</v>
+        <v>889</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kolmården, Ög</t>
+          <t>Klintaberget/Skybygget, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>566891.1650557418</v>
+        <v>566821</v>
       </c>
       <c r="R4" t="n">
-        <v>6521657.00191456</v>
+        <v>6521580</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +939,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2021-12-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-04-11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,28 +955,23 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Caroline Ryding</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
+          <t>Mikael Hagström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131996457</v>
+        <v>92007171</v>
       </c>
       <c r="B5" t="n">
         <v>91930</v>
@@ -1053,19 +1000,22 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skräpdalen, Ög</t>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>566774</v>
+        <v>566841</v>
       </c>
       <c r="R5" t="n">
-        <v>6521615</v>
+        <v>6521637</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,12 +1039,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2020-10-22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,21 +1053,860 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kaj Almqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>92007172</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>566801</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6521581</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-10-22</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kaj Almqvist</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>131996457</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91995</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Skräpdalen, Ög</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>566774</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6521615</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Jonatan Axelsson</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Jonatan Axelsson</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>97571065</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Klintaberget/Skybygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>566789</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6521591</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-04-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-04-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mikael Hagström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>92005698</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>566814</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6521570</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kaj Almqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>92005699</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>566759</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6521580</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Vesa Jussila</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>92005700</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Högsjön, Skybygget, Klintaberget, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>566833</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6521649</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Vesa Jussila</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Holmen</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>97569980</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Klintaberget/Skybygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>566758</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6521579</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kaj Almqvist</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>97569981</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Klintaberget/Skybygget, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>566832</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6521649</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Simonstorp</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-03-09</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Caroline Ryding</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kaj Almqvist</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21404-2024 artfynd.xlsx
+++ b/artfynd/A 21404-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100083913</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97571121</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97570874</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92007171</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92007172</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1275,6 +1305,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131996457</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1372,6 +1407,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97571065</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92005698</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1590,6 +1635,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92005699</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1699,6 +1749,11 @@
           <t>Holmen</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92005700</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1803,6 +1858,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97569980</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1907,8 +1967,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97569981</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>